--- a/artfynd/A 50304-2022 artfynd.xlsx
+++ b/artfynd/A 50304-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50304-2022 artfynd.xlsx
+++ b/artfynd/A 50304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109488967</v>
+        <v>110260327</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675846.4177085289</v>
+        <v>675765</v>
       </c>
       <c r="R2" t="n">
-        <v>7280439.922101423</v>
+        <v>7280600</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av tretåig hackspett på gran</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,59 +761,59 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Annika Lidström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109488926</v>
+        <v>110260473</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -839,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675867.080447775</v>
+        <v>675615</v>
       </c>
       <c r="R3" t="n">
-        <v>7280448.224992081</v>
+        <v>7280585</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,45 +870,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Annika Lidström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110260206</v>
+        <v>110260649</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675919.9575304504</v>
+        <v>675660</v>
       </c>
       <c r="R4" t="n">
-        <v>7280479.6283172</v>
+        <v>7280535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,19 +960,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110260680</v>
+        <v>110261361</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1094,13 +1032,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675660.07095134</v>
+        <v>676165</v>
       </c>
       <c r="R5" t="n">
-        <v>7280535.563534467</v>
+        <v>7280450</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,37 +1095,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110261460</v>
+        <v>110261504</v>
       </c>
       <c r="B6" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1506</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676099.937234754</v>
+        <v>676080</v>
       </c>
       <c r="R6" t="n">
-        <v>7280475.233084883</v>
+        <v>7280440</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,19 +1170,9 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,15 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110260306</v>
+        <v>110260251</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1334,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675814.8945759572</v>
+        <v>675865</v>
       </c>
       <c r="R7" t="n">
-        <v>7280569.421578153</v>
+        <v>7280450</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,19 +1275,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,15 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110260558</v>
+        <v>110260425</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675635.4738289427</v>
+        <v>675585</v>
       </c>
       <c r="R8" t="n">
-        <v>7280510.027055313</v>
+        <v>7280600</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,19 +1380,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,15 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110260225</v>
+        <v>110260454</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,27 +1421,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1574,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>675909.7835486304</v>
+        <v>675595</v>
       </c>
       <c r="R9" t="n">
-        <v>7280469.475099097</v>
+        <v>7280600</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,19 +1485,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,15 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110261361</v>
+        <v>110260558</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1694,13 +1557,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676164.9892225445</v>
+        <v>675635</v>
       </c>
       <c r="R10" t="n">
-        <v>7280449.75695904</v>
+        <v>7280510</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1724,22 +1587,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1767,15 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110260425</v>
+        <v>110260581</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>675585.2280005201</v>
+        <v>675645</v>
       </c>
       <c r="R11" t="n">
-        <v>7280599.422211331</v>
+        <v>7280510</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1847,19 +1695,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,15 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110261282</v>
+        <v>110260680</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1934,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676230.6180392652</v>
+        <v>675660</v>
       </c>
       <c r="R12" t="n">
-        <v>7280489.81917104</v>
+        <v>7280535</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,22 +1797,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2007,15 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110261532</v>
+        <v>110261319</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676070.2438064384</v>
+        <v>676230</v>
       </c>
       <c r="R13" t="n">
-        <v>7280444.821680367</v>
+        <v>7280445</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,19 +1905,9 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,15 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110260506</v>
+        <v>110261354</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,31 +1946,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2175,13 +1977,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>675629.4341162401</v>
+        <v>676165</v>
       </c>
       <c r="R14" t="n">
-        <v>7280500.125891969</v>
+        <v>7280450</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2205,27 +2007,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2234,6 +2021,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2252,15 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110260601</v>
+        <v>110261393</v>
       </c>
       <c r="B15" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2268,21 +2051,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2299,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>675654.5452363107</v>
+        <v>676130</v>
       </c>
       <c r="R15" t="n">
-        <v>7280510.355195801</v>
+        <v>7280475</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,22 +2112,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,15 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110261302</v>
+        <v>110261532</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,21 +2156,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2419,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676239.7320939545</v>
+        <v>676070</v>
       </c>
       <c r="R16" t="n">
-        <v>7280469.645686759</v>
+        <v>7280445</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2452,19 +2220,9 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2492,15 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110261473</v>
+        <v>110261745</v>
       </c>
       <c r="B17" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,21 +2261,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2539,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676099.937234754</v>
+        <v>676075</v>
       </c>
       <c r="R17" t="n">
-        <v>7280475.233084883</v>
+        <v>7280455</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2572,19 +2325,9 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2612,37 +2355,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110261504</v>
+        <v>110260888</v>
       </c>
       <c r="B18" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2659,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676080.5199388565</v>
+        <v>675665</v>
       </c>
       <c r="R18" t="n">
-        <v>7280439.642765212</v>
+        <v>7280530</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2689,22 +2427,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2732,15 +2460,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110261910</v>
+        <v>109488926</v>
       </c>
       <c r="B19" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,31 +2471,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2780,13 +2498,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676096.0533834111</v>
+        <v>675867</v>
       </c>
       <c r="R19" t="n">
-        <v>7280470.851153294</v>
+        <v>7280448</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2810,27 +2528,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack i basen på gran</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2839,33 +2542,44 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Heike Kontermann, Annika Lidström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110260454</v>
+        <v>110260290</v>
       </c>
       <c r="B20" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2873,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2904,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>675595.1768940123</v>
+        <v>675810</v>
       </c>
       <c r="R20" t="n">
-        <v>7280599.611201612</v>
+        <v>7280470</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2937,19 +2651,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2977,15 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110260609</v>
+        <v>110260601</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2993,27 +2692,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -3024,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>675654.5452363107</v>
+        <v>675655</v>
       </c>
       <c r="R21" t="n">
-        <v>7280510.355195801</v>
+        <v>7280510</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3057,19 +2756,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3097,15 +2786,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110261393</v>
+        <v>110261106</v>
       </c>
       <c r="B22" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3113,29 +2797,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3144,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676130</v>
+        <v>675690</v>
       </c>
       <c r="R22" t="n">
-        <v>7280475</v>
+        <v>7280545</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3174,12 +2854,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3207,15 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110261486</v>
+        <v>110261275</v>
       </c>
       <c r="B23" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3254,10 +2929,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>676089.87582062</v>
+        <v>676230</v>
       </c>
       <c r="R23" t="n">
-        <v>7280470.06078633</v>
+        <v>7280490</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3287,19 +2962,9 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3327,15 +2992,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110261964</v>
+        <v>110261486</v>
       </c>
       <c r="B24" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,31 +3003,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3375,13 +3034,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>675884.2592878346</v>
+        <v>676090</v>
       </c>
       <c r="R24" t="n">
-        <v>7280459.21828144</v>
+        <v>7280470</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3405,27 +3064,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack på gammal gran</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3434,6 +3078,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3452,37 +3097,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110261354</v>
+        <v>110261460</v>
       </c>
       <c r="B25" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3499,13 +3139,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676164.9892225445</v>
+        <v>676100</v>
       </c>
       <c r="R25" t="n">
-        <v>7280449.75695904</v>
+        <v>7280475</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3532,19 +3172,9 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3572,15 +3202,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110260251</v>
+        <v>110261223</v>
       </c>
       <c r="B26" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3588,29 +3213,25 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3619,10 +3240,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>675865.3009168429</v>
+        <v>676250</v>
       </c>
       <c r="R26" t="n">
-        <v>7280450.189701275</v>
+        <v>7280660</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3649,22 +3270,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar, vit mycel matta i marken under</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3692,41 +3308,40 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110261106</v>
+        <v>110261181</v>
       </c>
       <c r="B27" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3735,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>675690.2188880614</v>
+        <v>675695</v>
       </c>
       <c r="R27" t="n">
-        <v>7280544.855100686</v>
+        <v>7280545</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3768,19 +3383,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3808,19 +3413,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>110261431</v>
+        <v>110260225</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3855,10 +3455,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676105.0020915827</v>
+        <v>675910</v>
       </c>
       <c r="R28" t="n">
-        <v>7280460.20224895</v>
+        <v>7280470</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3885,22 +3485,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3928,43 +3518,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110260290</v>
+        <v>110260609</v>
       </c>
       <c r="B29" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3975,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>675810.1140213351</v>
+        <v>675655</v>
       </c>
       <c r="R29" t="n">
-        <v>7280470.467450392</v>
+        <v>7280510</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4008,19 +3593,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4048,43 +3623,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>110261275</v>
+        <v>110261431</v>
       </c>
       <c r="B30" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -4095,10 +3665,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676230.6180392652</v>
+        <v>676105</v>
       </c>
       <c r="R30" t="n">
-        <v>7280489.81917104</v>
+        <v>7280460</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4128,19 +3698,9 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4168,46 +3728,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>110260581</v>
+        <v>110261910</v>
       </c>
       <c r="B31" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4215,10 +3771,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>675645.423038156</v>
+        <v>676096</v>
       </c>
       <c r="R31" t="n">
-        <v>7280510.21620127</v>
+        <v>7280471</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4245,22 +3801,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack i basen på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4269,7 +3820,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4288,15 +3838,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>110260888</v>
+        <v>109488967</v>
       </c>
       <c r="B32" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4304,30 +3849,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4335,13 +3877,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>675665.3588325111</v>
+        <v>675846</v>
       </c>
       <c r="R32" t="n">
-        <v>7280530.49529985</v>
+        <v>7280440</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4365,22 +3907,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spår av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4389,61 +3926,60 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Heike Kontermann, Annika Lidström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>110261223</v>
+        <v>110260506</v>
       </c>
       <c r="B33" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4451,10 +3987,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676250.5682961219</v>
+        <v>675630</v>
       </c>
       <c r="R33" t="n">
-        <v>7280659.757381739</v>
+        <v>7280500</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4481,27 +4017,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkroppar, vit mycel matta i marken under</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4510,7 +4036,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4529,15 +4054,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>110261745</v>
+        <v>110261964</v>
       </c>
       <c r="B34" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4545,30 +4065,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4576,13 +4097,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>676075.0416689033</v>
+        <v>675884</v>
       </c>
       <c r="R34" t="n">
-        <v>7280454.64859048</v>
+        <v>7280459</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4606,22 +4127,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4630,7 +4146,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4649,15 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>110261319</v>
+        <v>109600942</v>
       </c>
       <c r="B35" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4665,30 +4175,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4696,13 +4215,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676230.0508461401</v>
+        <v>675827</v>
       </c>
       <c r="R35" t="n">
-        <v>7280444.596607687</v>
+        <v>7280463</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4726,22 +4245,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4750,502 +4269,21 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Annika Lidström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Annika Lidström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>110260473</v>
-      </c>
-      <c r="B36" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>658</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Rullholmen, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>675615.5883526852</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7280584.682483152</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>110260649</v>
-      </c>
-      <c r="B37" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>658</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Rullholmen, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>675660.07095134</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7280535.563534467</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>110261181</v>
-      </c>
-      <c r="B38" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Rullholmen, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>675695.2059727855</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7280544.743253341</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>110260327</v>
-      </c>
-      <c r="B39" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>658</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Rullholmen, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>675765.3358914485</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7280599.575330046</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50304-2022 artfynd.xlsx
+++ b/artfynd/A 50304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260327</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260473</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260649</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261361</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261504</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260251</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260425</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260454</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260558</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260581</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260680</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1932,6 +1992,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261319</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2037,6 +2102,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261354</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2142,6 +2212,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261393</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2247,6 +2322,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261532</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2352,6 +2432,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261745</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2457,6 +2542,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260888</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2573,6 +2663,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109488926</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2678,6 +2773,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260290</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2783,6 +2883,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260601</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2884,6 +2989,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261106</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2989,6 +3099,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261275</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3094,6 +3209,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261486</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3199,6 +3319,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261460</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3305,6 +3430,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261223</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3410,6 +3540,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261181</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3515,6 +3650,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260225</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3620,6 +3760,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260609</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3725,6 +3870,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261431</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3835,6 +3985,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261910</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3941,6 +4096,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109488967</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4051,6 +4211,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110260506</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4161,6 +4326,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110261964</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4284,8 +4454,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109600942</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>